--- a/src/technology/small-modular-reactor/small-modular-reactor.xlsx
+++ b/src/technology/small-modular-reactor/small-modular-reactor.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rhanes\GitHub\tyche\src\technology\small-modular-reactor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A373153-E7A6-4794-A1AE-BE0C068B8880}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D019919-EF52-4B91-97A0-3761398A9FC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="26145" yWindow="1545" windowWidth="25260" windowHeight="17685" activeTab="7" xr2:uid="{277ED3FD-2B20-4A36-BB03-16AF83BDC75C}"/>
+    <workbookView xWindow="1875" yWindow="1620" windowWidth="25185" windowHeight="17685" tabRatio="778" activeTab="4" xr2:uid="{277ED3FD-2B20-4A36-BB03-16AF83BDC75C}"/>
   </bookViews>
   <sheets>
     <sheet name="indices" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">designs!$A$1:$G$911</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">indices!$A$1:$F$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">parameters!$A$1:$G$205</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">parameters!$A$1:$G$217</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1552" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1613" uniqueCount="149">
   <si>
     <t>Category</t>
   </si>
@@ -2423,7 +2423,8 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9375A35C-8A58-4D70-9436-2E641DE51D25}">
-  <dimension ref="A1:G205"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:G217"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.42578125" bestFit="1" customWidth="1"/>
@@ -3011,7 +3012,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>39</v>
       </c>
@@ -3034,7 +3035,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>39</v>
       </c>
@@ -3057,7 +3058,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>39</v>
       </c>
@@ -3080,7 +3081,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>39</v>
       </c>
@@ -3103,7 +3104,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>39</v>
       </c>
@@ -3126,7 +3127,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>39</v>
       </c>
@@ -3149,7 +3150,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>39</v>
       </c>
@@ -3172,7 +3173,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>39</v>
       </c>
@@ -3195,7 +3196,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>39</v>
       </c>
@@ -3218,7 +3219,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>39</v>
       </c>
@@ -3241,7 +3242,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>39</v>
       </c>
@@ -3264,7 +3265,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>39</v>
       </c>
@@ -3287,7 +3288,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>39</v>
       </c>
@@ -3310,7 +3311,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>39</v>
       </c>
@@ -3333,7 +3334,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>39</v>
       </c>
@@ -3356,7 +3357,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>39</v>
       </c>
@@ -3379,7 +3380,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>39</v>
       </c>
@@ -3402,7 +3403,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>39</v>
       </c>
@@ -3425,7 +3426,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>39</v>
       </c>
@@ -3448,7 +3449,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>39</v>
       </c>
@@ -3471,7 +3472,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>39</v>
       </c>
@@ -3494,76 +3495,76 @@
         <v>67</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>39</v>
       </c>
       <c r="B47" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C47" t="s">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="D47">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E47">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="F47" t="s">
-        <v>43</v>
+        <v>91</v>
       </c>
       <c r="G47" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>39</v>
       </c>
       <c r="B48" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C48" t="s">
-        <v>63</v>
+        <v>90</v>
       </c>
       <c r="D48">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="E48">
-        <v>1</v>
+        <v>179</v>
       </c>
       <c r="F48" t="s">
-        <v>43</v>
+        <v>92</v>
       </c>
       <c r="G48" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>39</v>
       </c>
       <c r="B49" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C49" t="s">
-        <v>54</v>
+        <v>95</v>
       </c>
       <c r="D49">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="E49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F49" t="s">
-        <v>43</v>
+        <v>91</v>
       </c>
       <c r="G49" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>39</v>
       </c>
@@ -3571,10 +3572,10 @@
         <v>87</v>
       </c>
       <c r="C50" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D50">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E50">
         <v>2</v>
@@ -3583,10 +3584,10 @@
         <v>43</v>
       </c>
       <c r="G50" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>39</v>
       </c>
@@ -3594,22 +3595,22 @@
         <v>87</v>
       </c>
       <c r="C51" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="D51">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F51" t="s">
         <v>43</v>
       </c>
       <c r="G51" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>39</v>
       </c>
@@ -3617,22 +3618,22 @@
         <v>87</v>
       </c>
       <c r="C52" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="D52">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E52">
-        <v>22000</v>
+        <v>2</v>
       </c>
       <c r="F52" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G52" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>39</v>
       </c>
@@ -3640,22 +3641,22 @@
         <v>87</v>
       </c>
       <c r="C53" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D53">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E53">
-        <v>0.4</v>
+        <v>2</v>
       </c>
       <c r="F53" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G53" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>39</v>
       </c>
@@ -3663,22 +3664,22 @@
         <v>87</v>
       </c>
       <c r="C54" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D54">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E54">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F54" t="s">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="G54" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>39</v>
       </c>
@@ -3686,22 +3687,22 @@
         <v>87</v>
       </c>
       <c r="C55" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D55">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E55">
-        <v>0.06</v>
+        <v>22000</v>
       </c>
       <c r="F55" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G55" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>39</v>
       </c>
@@ -3709,22 +3710,22 @@
         <v>87</v>
       </c>
       <c r="C56" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D56">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E56">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="F56" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G56" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>39</v>
       </c>
@@ -3732,22 +3733,22 @@
         <v>87</v>
       </c>
       <c r="C57" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D57">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E57">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F57" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="G57" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>39</v>
       </c>
@@ -3755,22 +3756,22 @@
         <v>87</v>
       </c>
       <c r="C58" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="D58">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E58">
-        <v>1</v>
+        <v>0.06</v>
       </c>
       <c r="F58" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G58" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>39</v>
       </c>
@@ -3778,10 +3779,10 @@
         <v>87</v>
       </c>
       <c r="C59" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="D59">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E59">
         <v>1</v>
@@ -3790,10 +3791,10 @@
         <v>43</v>
       </c>
       <c r="G59" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>39</v>
       </c>
@@ -3801,22 +3802,22 @@
         <v>87</v>
       </c>
       <c r="C60" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="D60">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E60">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F60" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G60" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>39</v>
       </c>
@@ -3824,22 +3825,22 @@
         <v>87</v>
       </c>
       <c r="C61" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="D61">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E61">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="F61" t="s">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="G61" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>39</v>
       </c>
@@ -3847,22 +3848,22 @@
         <v>87</v>
       </c>
       <c r="C62" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="D62">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E62">
         <v>1</v>
       </c>
       <c r="F62" t="s">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="G62" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>39</v>
       </c>
@@ -3870,22 +3871,22 @@
         <v>87</v>
       </c>
       <c r="C63" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="D63">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E63">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F63" t="s">
-        <v>72</v>
+        <v>44</v>
       </c>
       <c r="G63" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>39</v>
       </c>
@@ -3893,22 +3894,22 @@
         <v>87</v>
       </c>
       <c r="C64" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D64">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E64">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="F64" t="s">
         <v>72</v>
       </c>
       <c r="G64" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>39</v>
       </c>
@@ -3916,10 +3917,10 @@
         <v>87</v>
       </c>
       <c r="C65" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D65">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E65">
         <v>1</v>
@@ -3928,10 +3929,10 @@
         <v>72</v>
       </c>
       <c r="G65" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>39</v>
       </c>
@@ -3939,22 +3940,22 @@
         <v>87</v>
       </c>
       <c r="C66" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="D66">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E66">
-        <v>250000000</v>
+        <v>1</v>
       </c>
       <c r="F66" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G66" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>39</v>
       </c>
@@ -3962,160 +3963,160 @@
         <v>87</v>
       </c>
       <c r="C67" t="s">
+        <v>48</v>
+      </c>
+      <c r="D67">
+        <v>17</v>
+      </c>
+      <c r="E67">
+        <v>1</v>
+      </c>
+      <c r="F67" t="s">
+        <v>72</v>
+      </c>
+      <c r="G67" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>39</v>
+      </c>
+      <c r="B68" t="s">
+        <v>87</v>
+      </c>
+      <c r="C68" t="s">
+        <v>49</v>
+      </c>
+      <c r="D68">
+        <v>18</v>
+      </c>
+      <c r="E68">
+        <v>1</v>
+      </c>
+      <c r="F68" t="s">
+        <v>72</v>
+      </c>
+      <c r="G68" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>39</v>
+      </c>
+      <c r="B69" t="s">
+        <v>87</v>
+      </c>
+      <c r="C69" t="s">
+        <v>68</v>
+      </c>
+      <c r="D69">
+        <v>19</v>
+      </c>
+      <c r="E69">
+        <v>250000000</v>
+      </c>
+      <c r="F69" t="s">
+        <v>73</v>
+      </c>
+      <c r="G69" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>39</v>
+      </c>
+      <c r="B70" t="s">
+        <v>87</v>
+      </c>
+      <c r="C70" t="s">
         <v>69</v>
       </c>
-      <c r="D67">
+      <c r="D70">
         <v>20</v>
       </c>
-      <c r="E67">
+      <c r="E70">
         <v>150000000</v>
       </c>
-      <c r="F67" t="s">
+      <c r="F70" t="s">
         <v>73</v>
       </c>
-      <c r="G67" t="s">
+      <c r="G70" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>39</v>
-      </c>
-      <c r="B68" t="s">
-        <v>106</v>
-      </c>
-      <c r="C68" t="s">
-        <v>59</v>
-      </c>
-      <c r="D68">
-        <v>0</v>
-      </c>
-      <c r="E68">
-        <v>2</v>
-      </c>
-      <c r="F68" t="s">
-        <v>43</v>
-      </c>
-      <c r="G68" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>39</v>
-      </c>
-      <c r="B69" t="s">
-        <v>106</v>
-      </c>
-      <c r="C69" t="s">
-        <v>63</v>
-      </c>
-      <c r="D69">
-        <v>1</v>
-      </c>
-      <c r="E69">
-        <v>1</v>
-      </c>
-      <c r="F69" t="s">
-        <v>43</v>
-      </c>
-      <c r="G69" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>39</v>
-      </c>
-      <c r="B70" t="s">
-        <v>106</v>
-      </c>
-      <c r="C70" t="s">
-        <v>54</v>
-      </c>
-      <c r="D70">
-        <v>2</v>
-      </c>
-      <c r="E70">
-        <v>2</v>
-      </c>
-      <c r="F70" t="s">
-        <v>43</v>
-      </c>
-      <c r="G70" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>39</v>
       </c>
       <c r="B71" t="s">
-        <v>106</v>
+        <v>87</v>
       </c>
       <c r="C71" t="s">
-        <v>55</v>
+        <v>89</v>
       </c>
       <c r="D71">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="E71">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="F71" t="s">
-        <v>43</v>
+        <v>91</v>
       </c>
       <c r="G71" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>39</v>
       </c>
       <c r="B72" t="s">
-        <v>106</v>
+        <v>87</v>
       </c>
       <c r="C72" t="s">
-        <v>56</v>
+        <v>90</v>
       </c>
       <c r="D72">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="E72">
-        <v>2</v>
+        <v>179</v>
       </c>
       <c r="F72" t="s">
-        <v>43</v>
+        <v>92</v>
       </c>
       <c r="G72" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>39</v>
       </c>
       <c r="B73" t="s">
-        <v>106</v>
+        <v>87</v>
       </c>
       <c r="C73" t="s">
-        <v>64</v>
+        <v>95</v>
       </c>
       <c r="D73">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="E73">
-        <v>22000</v>
+        <v>1</v>
       </c>
       <c r="F73" t="s">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="G73" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>39</v>
       </c>
@@ -4123,22 +4124,22 @@
         <v>106</v>
       </c>
       <c r="C74" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D74">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E74">
-        <v>0.4</v>
+        <v>2</v>
       </c>
       <c r="F74" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G74" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>39</v>
       </c>
@@ -4146,22 +4147,22 @@
         <v>106</v>
       </c>
       <c r="C75" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D75">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E75">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F75" t="s">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="G75" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>39</v>
       </c>
@@ -4169,22 +4170,22 @@
         <v>106</v>
       </c>
       <c r="C76" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="D76">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E76">
-        <v>0.06</v>
+        <v>2</v>
       </c>
       <c r="F76" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G76" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>39</v>
       </c>
@@ -4192,22 +4193,22 @@
         <v>106</v>
       </c>
       <c r="C77" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D77">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E77">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F77" t="s">
         <v>43</v>
       </c>
       <c r="G77" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>39</v>
       </c>
@@ -4215,22 +4216,22 @@
         <v>106</v>
       </c>
       <c r="C78" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D78">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E78">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F78" t="s">
         <v>43</v>
       </c>
       <c r="G78" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>39</v>
       </c>
@@ -4238,22 +4239,22 @@
         <v>106</v>
       </c>
       <c r="C79" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="D79">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E79">
-        <v>1</v>
+        <v>22000</v>
       </c>
       <c r="F79" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G79" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>39</v>
       </c>
@@ -4261,22 +4262,22 @@
         <v>106</v>
       </c>
       <c r="C80" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="D80">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E80">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="F80" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G80" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>39</v>
       </c>
@@ -4284,22 +4285,22 @@
         <v>106</v>
       </c>
       <c r="C81" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="D81">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E81">
         <v>3</v>
       </c>
       <c r="F81" t="s">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="G81" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>39</v>
       </c>
@@ -4307,22 +4308,22 @@
         <v>106</v>
       </c>
       <c r="C82" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="D82">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E82">
-        <v>13</v>
+        <v>0.06</v>
       </c>
       <c r="F82" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="G82" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>39</v>
       </c>
@@ -4330,22 +4331,22 @@
         <v>106</v>
       </c>
       <c r="C83" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D83">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E83">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="F83" t="s">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="G83" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>39</v>
       </c>
@@ -4353,22 +4354,22 @@
         <v>106</v>
       </c>
       <c r="C84" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="D84">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E84">
         <v>1</v>
       </c>
       <c r="F84" t="s">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="G84" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>39</v>
       </c>
@@ -4376,22 +4377,22 @@
         <v>106</v>
       </c>
       <c r="C85" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="D85">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E85">
         <v>1</v>
       </c>
       <c r="F85" t="s">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="G85" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>39</v>
       </c>
@@ -4399,22 +4400,22 @@
         <v>106</v>
       </c>
       <c r="C86" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="D86">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E86">
         <v>1</v>
       </c>
       <c r="F86" t="s">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="G86" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>39</v>
       </c>
@@ -4422,22 +4423,22 @@
         <v>106</v>
       </c>
       <c r="C87" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D87">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E87">
-        <v>250000000</v>
+        <v>3</v>
       </c>
       <c r="F87" t="s">
-        <v>73</v>
+        <v>44</v>
       </c>
       <c r="G87" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>39</v>
       </c>
@@ -4445,229 +4446,229 @@
         <v>106</v>
       </c>
       <c r="C88" t="s">
+        <v>45</v>
+      </c>
+      <c r="D88">
+        <v>14</v>
+      </c>
+      <c r="E88">
+        <v>13</v>
+      </c>
+      <c r="F88" t="s">
+        <v>72</v>
+      </c>
+      <c r="G88" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>39</v>
+      </c>
+      <c r="B89" t="s">
+        <v>106</v>
+      </c>
+      <c r="C89" t="s">
+        <v>53</v>
+      </c>
+      <c r="D89">
+        <v>15</v>
+      </c>
+      <c r="E89">
+        <v>13</v>
+      </c>
+      <c r="F89" t="s">
+        <v>72</v>
+      </c>
+      <c r="G89" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>39</v>
+      </c>
+      <c r="B90" t="s">
+        <v>106</v>
+      </c>
+      <c r="C90" t="s">
+        <v>47</v>
+      </c>
+      <c r="D90">
+        <v>16</v>
+      </c>
+      <c r="E90">
+        <v>1</v>
+      </c>
+      <c r="F90" t="s">
+        <v>72</v>
+      </c>
+      <c r="G90" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>39</v>
+      </c>
+      <c r="B91" t="s">
+        <v>106</v>
+      </c>
+      <c r="C91" t="s">
+        <v>48</v>
+      </c>
+      <c r="D91">
+        <v>17</v>
+      </c>
+      <c r="E91">
+        <v>1</v>
+      </c>
+      <c r="F91" t="s">
+        <v>72</v>
+      </c>
+      <c r="G91" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>39</v>
+      </c>
+      <c r="B92" t="s">
+        <v>106</v>
+      </c>
+      <c r="C92" t="s">
+        <v>49</v>
+      </c>
+      <c r="D92">
+        <v>18</v>
+      </c>
+      <c r="E92">
+        <v>1</v>
+      </c>
+      <c r="F92" t="s">
+        <v>72</v>
+      </c>
+      <c r="G92" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>39</v>
+      </c>
+      <c r="B93" t="s">
+        <v>106</v>
+      </c>
+      <c r="C93" t="s">
+        <v>68</v>
+      </c>
+      <c r="D93">
+        <v>19</v>
+      </c>
+      <c r="E93">
+        <v>250000000</v>
+      </c>
+      <c r="F93" t="s">
+        <v>73</v>
+      </c>
+      <c r="G93" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>39</v>
+      </c>
+      <c r="B94" t="s">
+        <v>106</v>
+      </c>
+      <c r="C94" t="s">
         <v>69</v>
       </c>
-      <c r="D88">
+      <c r="D94">
         <v>20</v>
       </c>
-      <c r="E88">
+      <c r="E94">
         <v>150000000</v>
       </c>
-      <c r="F88" t="s">
+      <c r="F94" t="s">
         <v>73</v>
       </c>
-      <c r="G88" t="s">
+      <c r="G94" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
-        <v>39</v>
-      </c>
-      <c r="B89" t="s">
-        <v>105</v>
-      </c>
-      <c r="C89" t="s">
-        <v>59</v>
-      </c>
-      <c r="D89">
-        <v>0</v>
-      </c>
-      <c r="E89">
-        <v>0</v>
-      </c>
-      <c r="F89" t="s">
-        <v>43</v>
-      </c>
-      <c r="G89" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
-        <v>39</v>
-      </c>
-      <c r="B90" t="s">
-        <v>105</v>
-      </c>
-      <c r="C90" t="s">
-        <v>63</v>
-      </c>
-      <c r="D90">
-        <v>1</v>
-      </c>
-      <c r="E90">
-        <v>0</v>
-      </c>
-      <c r="F90" t="s">
-        <v>43</v>
-      </c>
-      <c r="G90" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
-        <v>39</v>
-      </c>
-      <c r="B91" t="s">
-        <v>105</v>
-      </c>
-      <c r="C91" t="s">
-        <v>54</v>
-      </c>
-      <c r="D91">
-        <v>2</v>
-      </c>
-      <c r="E91">
-        <v>0</v>
-      </c>
-      <c r="F91" t="s">
-        <v>43</v>
-      </c>
-      <c r="G91" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
-        <v>39</v>
-      </c>
-      <c r="B92" t="s">
-        <v>105</v>
-      </c>
-      <c r="C92" t="s">
-        <v>55</v>
-      </c>
-      <c r="D92">
-        <v>3</v>
-      </c>
-      <c r="E92">
-        <v>0</v>
-      </c>
-      <c r="F92" t="s">
-        <v>43</v>
-      </c>
-      <c r="G92" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
-        <v>39</v>
-      </c>
-      <c r="B93" t="s">
-        <v>105</v>
-      </c>
-      <c r="C93" t="s">
-        <v>56</v>
-      </c>
-      <c r="D93">
-        <v>4</v>
-      </c>
-      <c r="E93">
-        <v>0</v>
-      </c>
-      <c r="F93" t="s">
-        <v>43</v>
-      </c>
-      <c r="G93" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>39</v>
-      </c>
-      <c r="B94" t="s">
-        <v>105</v>
-      </c>
-      <c r="C94" t="s">
-        <v>64</v>
-      </c>
-      <c r="D94">
-        <v>5</v>
-      </c>
-      <c r="E94">
-        <v>1000000</v>
-      </c>
-      <c r="F94" t="s">
-        <v>41</v>
-      </c>
-      <c r="G94" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>39</v>
       </c>
       <c r="B95" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C95" t="s">
-        <v>61</v>
+        <v>89</v>
       </c>
       <c r="D95">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="E95">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F95" t="s">
-        <v>42</v>
+        <v>91</v>
       </c>
       <c r="G95" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>39</v>
       </c>
       <c r="B96" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C96" t="s">
-        <v>62</v>
+        <v>90</v>
       </c>
       <c r="D96">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="E96">
-        <v>13</v>
+        <v>179</v>
       </c>
       <c r="F96" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="G96" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>39</v>
       </c>
       <c r="B97" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C97" t="s">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="D97">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="E97">
-        <v>0.15</v>
+        <v>1</v>
       </c>
       <c r="F97" t="s">
-        <v>42</v>
+        <v>91</v>
       </c>
       <c r="G97" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>39</v>
       </c>
@@ -4675,10 +4676,10 @@
         <v>105</v>
       </c>
       <c r="C98" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D98">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E98">
         <v>0</v>
@@ -4687,10 +4688,10 @@
         <v>43</v>
       </c>
       <c r="G98" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>39</v>
       </c>
@@ -4698,10 +4699,10 @@
         <v>105</v>
       </c>
       <c r="C99" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D99">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -4710,10 +4711,10 @@
         <v>43</v>
       </c>
       <c r="G99" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>39</v>
       </c>
@@ -4721,10 +4722,10 @@
         <v>105</v>
       </c>
       <c r="C100" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D100">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -4733,10 +4734,10 @@
         <v>43</v>
       </c>
       <c r="G100" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>39</v>
       </c>
@@ -4744,22 +4745,22 @@
         <v>105</v>
       </c>
       <c r="C101" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="D101">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E101">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="F101" t="s">
         <v>43</v>
       </c>
       <c r="G101" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>39</v>
       </c>
@@ -4767,22 +4768,22 @@
         <v>105</v>
       </c>
       <c r="C102" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="D102">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E102">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="F102" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G102" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>39</v>
       </c>
@@ -4790,22 +4791,22 @@
         <v>105</v>
       </c>
       <c r="C103" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="D103">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E103">
-        <v>13</v>
+        <v>1000000</v>
       </c>
       <c r="F103" t="s">
-        <v>72</v>
+        <v>41</v>
       </c>
       <c r="G103" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>39</v>
       </c>
@@ -4813,22 +4814,22 @@
         <v>105</v>
       </c>
       <c r="C104" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D104">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E104">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="F104" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="G104" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>39</v>
       </c>
@@ -4836,10 +4837,10 @@
         <v>105</v>
       </c>
       <c r="C105" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="D105">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E105">
         <v>13</v>
@@ -4848,10 +4849,10 @@
         <v>72</v>
       </c>
       <c r="G105" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>39</v>
       </c>
@@ -4859,22 +4860,22 @@
         <v>105</v>
       </c>
       <c r="C106" t="s">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="D106">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E106">
-        <v>13</v>
+        <v>0.15</v>
       </c>
       <c r="F106" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="G106" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>39</v>
       </c>
@@ -4882,22 +4883,22 @@
         <v>105</v>
       </c>
       <c r="C107" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="D107">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E107">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="F107" t="s">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="G107" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>39</v>
       </c>
@@ -4905,22 +4906,22 @@
         <v>105</v>
       </c>
       <c r="C108" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D108">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E108">
-        <v>250000000</v>
+        <v>0</v>
       </c>
       <c r="F108" t="s">
-        <v>73</v>
+        <v>43</v>
       </c>
       <c r="G108" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>39</v>
       </c>
@@ -4928,298 +4929,298 @@
         <v>105</v>
       </c>
       <c r="C109" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="D109">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E109">
-        <v>150000000</v>
+        <v>0</v>
       </c>
       <c r="F109" t="s">
-        <v>73</v>
+        <v>43</v>
       </c>
       <c r="G109" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>39</v>
       </c>
       <c r="B110" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C110" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="D110">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E110">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="F110" t="s">
         <v>43</v>
       </c>
       <c r="G110" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>39</v>
       </c>
       <c r="B111" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C111" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="D111">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="E111">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="F111" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G111" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>39</v>
       </c>
       <c r="B112" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C112" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="D112">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="E112">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="F112" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="G112" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>39</v>
       </c>
       <c r="B113" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C113" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D113">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E113">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="F113" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="G113" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>39</v>
       </c>
       <c r="B114" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C114" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="D114">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="E114">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="F114" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="G114" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>39</v>
       </c>
       <c r="B115" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C115" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="D115">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E115">
-        <v>22000</v>
+        <v>13</v>
       </c>
       <c r="F115" t="s">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="G115" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>39</v>
       </c>
       <c r="B116" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C116" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="D116">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E116">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F116" t="s">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="G116" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>39</v>
       </c>
       <c r="B117" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C117" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="D117">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E117">
-        <v>3</v>
+        <v>250000000</v>
       </c>
       <c r="F117" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G117" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>39</v>
       </c>
       <c r="B118" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C118" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D118">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E118">
-        <v>0.06</v>
+        <v>150000000</v>
       </c>
       <c r="F118" t="s">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="G118" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>39</v>
       </c>
       <c r="B119" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C119" t="s">
-        <v>58</v>
+        <v>89</v>
       </c>
       <c r="D119">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E119">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="F119" t="s">
-        <v>43</v>
+        <v>91</v>
       </c>
       <c r="G119" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>39</v>
       </c>
       <c r="B120" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C120" t="s">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="D120">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E120">
-        <v>1</v>
+        <v>179</v>
       </c>
       <c r="F120" t="s">
-        <v>43</v>
+        <v>92</v>
       </c>
       <c r="G120" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>39</v>
       </c>
       <c r="B121" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C121" t="s">
-        <v>57</v>
+        <v>95</v>
       </c>
       <c r="D121">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E121">
         <v>1</v>
       </c>
       <c r="F121" t="s">
-        <v>43</v>
+        <v>91</v>
       </c>
       <c r="G121" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>39</v>
       </c>
@@ -5227,22 +5228,22 @@
         <v>107</v>
       </c>
       <c r="C122" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="D122">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E122">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="F122" t="s">
         <v>43</v>
       </c>
       <c r="G122" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>39</v>
       </c>
@@ -5250,22 +5251,22 @@
         <v>107</v>
       </c>
       <c r="C123" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D123">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E123">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="F123" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G123" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>39</v>
       </c>
@@ -5273,22 +5274,22 @@
         <v>107</v>
       </c>
       <c r="C124" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="D124">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="E124">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="F124" t="s">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="G124" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>39</v>
       </c>
@@ -5296,22 +5297,22 @@
         <v>107</v>
       </c>
       <c r="C125" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D125">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="E125">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="F125" t="s">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="G125" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>39</v>
       </c>
@@ -5319,22 +5320,22 @@
         <v>107</v>
       </c>
       <c r="C126" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="D126">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="E126">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F126" t="s">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="G126" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>39</v>
       </c>
@@ -5342,22 +5343,22 @@
         <v>107</v>
       </c>
       <c r="C127" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="D127">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E127">
-        <v>3</v>
+        <v>22000</v>
       </c>
       <c r="F127" t="s">
-        <v>72</v>
+        <v>41</v>
       </c>
       <c r="G127" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>39</v>
       </c>
@@ -5365,22 +5366,22 @@
         <v>107</v>
       </c>
       <c r="C128" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="D128">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E128">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F128" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="G128" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>39</v>
       </c>
@@ -5388,22 +5389,22 @@
         <v>107</v>
       </c>
       <c r="C129" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D129">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E129">
-        <v>250000000</v>
+        <v>3</v>
       </c>
       <c r="F129" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G129" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>39</v>
       </c>
@@ -5411,22 +5412,22 @@
         <v>107</v>
       </c>
       <c r="C130" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D130">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E130">
-        <v>150000000</v>
+        <v>0.06</v>
       </c>
       <c r="F130" t="s">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="G130" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>39</v>
       </c>
@@ -5434,22 +5435,22 @@
         <v>107</v>
       </c>
       <c r="C131" t="s">
-        <v>89</v>
+        <v>58</v>
       </c>
       <c r="D131">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="E131">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="F131" t="s">
-        <v>91</v>
+        <v>43</v>
       </c>
       <c r="G131" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>39</v>
       </c>
@@ -5457,22 +5458,22 @@
         <v>107</v>
       </c>
       <c r="C132" t="s">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="D132">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E132">
-        <v>179</v>
+        <v>1</v>
       </c>
       <c r="F132" t="s">
-        <v>92</v>
+        <v>43</v>
       </c>
       <c r="G132" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>39</v>
       </c>
@@ -5480,298 +5481,298 @@
         <v>107</v>
       </c>
       <c r="C133" t="s">
-        <v>95</v>
+        <v>57</v>
       </c>
       <c r="D133">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="E133">
         <v>1</v>
       </c>
       <c r="F133" t="s">
-        <v>91</v>
+        <v>43</v>
       </c>
       <c r="G133" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>39</v>
       </c>
       <c r="B134" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C134" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="D134">
-        <v>0</v>
-      </c>
-      <c r="E134" t="s">
-        <v>130</v>
+        <v>12</v>
+      </c>
+      <c r="E134">
+        <v>0.7</v>
       </c>
       <c r="F134" t="s">
         <v>43</v>
       </c>
       <c r="G134" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>39</v>
       </c>
       <c r="B135" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C135" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="D135">
-        <v>1</v>
-      </c>
-      <c r="E135" t="s">
-        <v>131</v>
+        <v>13</v>
+      </c>
+      <c r="E135">
+        <v>16</v>
       </c>
       <c r="F135" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G135" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>39</v>
       </c>
       <c r="B136" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C136" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="D136">
-        <v>2</v>
-      </c>
-      <c r="E136" t="s">
-        <v>132</v>
+        <v>14</v>
+      </c>
+      <c r="E136">
+        <v>13</v>
       </c>
       <c r="F136" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="G136" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>39</v>
       </c>
       <c r="B137" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C137" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D137">
+        <v>15</v>
+      </c>
+      <c r="E137">
+        <v>13</v>
+      </c>
+      <c r="F137" t="s">
+        <v>72</v>
+      </c>
+      <c r="G137" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>39</v>
+      </c>
+      <c r="B138" t="s">
+        <v>107</v>
+      </c>
+      <c r="C138" t="s">
+        <v>47</v>
+      </c>
+      <c r="D138">
+        <v>16</v>
+      </c>
+      <c r="E138">
+        <v>4</v>
+      </c>
+      <c r="F138" t="s">
+        <v>72</v>
+      </c>
+      <c r="G138" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>39</v>
+      </c>
+      <c r="B139" t="s">
+        <v>107</v>
+      </c>
+      <c r="C139" t="s">
+        <v>48</v>
+      </c>
+      <c r="D139">
+        <v>17</v>
+      </c>
+      <c r="E139">
         <v>3</v>
       </c>
-      <c r="E137" t="s">
-        <v>132</v>
-      </c>
-      <c r="F137" t="s">
-        <v>43</v>
-      </c>
-      <c r="G137" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A138" t="s">
-        <v>39</v>
-      </c>
-      <c r="B138" t="s">
-        <v>108</v>
-      </c>
-      <c r="C138" t="s">
-        <v>56</v>
-      </c>
-      <c r="D138">
-        <v>4</v>
-      </c>
-      <c r="E138" t="s">
-        <v>130</v>
-      </c>
-      <c r="F138" t="s">
-        <v>43</v>
-      </c>
-      <c r="G138" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A139" t="s">
-        <v>39</v>
-      </c>
-      <c r="B139" t="s">
-        <v>108</v>
-      </c>
-      <c r="C139" t="s">
-        <v>64</v>
-      </c>
-      <c r="D139">
+      <c r="F139" t="s">
+        <v>72</v>
+      </c>
+      <c r="G139" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>39</v>
+      </c>
+      <c r="B140" t="s">
+        <v>107</v>
+      </c>
+      <c r="C140" t="s">
+        <v>49</v>
+      </c>
+      <c r="D140">
+        <v>18</v>
+      </c>
+      <c r="E140">
         <v>5</v>
       </c>
-      <c r="E139" t="s">
-        <v>138</v>
-      </c>
-      <c r="F139" t="s">
-        <v>41</v>
-      </c>
-      <c r="G139" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A140" t="s">
-        <v>39</v>
-      </c>
-      <c r="B140" t="s">
-        <v>108</v>
-      </c>
-      <c r="C140" t="s">
-        <v>61</v>
-      </c>
-      <c r="D140">
-        <v>6</v>
-      </c>
-      <c r="E140" t="s">
-        <v>139</v>
-      </c>
       <c r="F140" t="s">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="G140" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>39</v>
       </c>
       <c r="B141" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C141" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="D141">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E141">
-        <v>3</v>
+        <v>250000000</v>
       </c>
       <c r="F141" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G141" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>39</v>
       </c>
       <c r="B142" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C142" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D142">
-        <v>8</v>
-      </c>
-      <c r="E142" t="s">
-        <v>140</v>
+        <v>20</v>
+      </c>
+      <c r="E142">
+        <v>150000000</v>
       </c>
       <c r="F142" t="s">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="G142" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>39</v>
       </c>
       <c r="B143" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C143" t="s">
-        <v>58</v>
+        <v>89</v>
       </c>
       <c r="D143">
-        <v>9</v>
-      </c>
-      <c r="E143" t="s">
-        <v>127</v>
+        <v>21</v>
+      </c>
+      <c r="E143">
+        <v>13</v>
       </c>
       <c r="F143" t="s">
-        <v>43</v>
+        <v>91</v>
       </c>
       <c r="G143" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>39</v>
       </c>
       <c r="B144" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C144" t="s">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="D144">
-        <v>10</v>
-      </c>
-      <c r="E144" t="s">
-        <v>127</v>
+        <v>22</v>
+      </c>
+      <c r="E144">
+        <v>179</v>
       </c>
       <c r="F144" t="s">
-        <v>43</v>
+        <v>92</v>
       </c>
       <c r="G144" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>39</v>
       </c>
       <c r="B145" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C145" t="s">
-        <v>57</v>
+        <v>95</v>
       </c>
       <c r="D145">
-        <v>11</v>
-      </c>
-      <c r="E145" t="s">
-        <v>127</v>
+        <v>23</v>
+      </c>
+      <c r="E145">
+        <v>1</v>
       </c>
       <c r="F145" t="s">
-        <v>43</v>
+        <v>91</v>
       </c>
       <c r="G145" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>39</v>
       </c>
@@ -5779,22 +5780,22 @@
         <v>108</v>
       </c>
       <c r="C146" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="D146">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E146" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="F146" t="s">
         <v>43</v>
       </c>
       <c r="G146" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>39</v>
       </c>
@@ -5802,22 +5803,22 @@
         <v>108</v>
       </c>
       <c r="C147" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D147">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E147" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F147" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G147" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>39</v>
       </c>
@@ -5825,22 +5826,22 @@
         <v>108</v>
       </c>
       <c r="C148" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="D148">
-        <v>14</v>
-      </c>
-      <c r="E148">
-        <v>13</v>
+        <v>2</v>
+      </c>
+      <c r="E148" t="s">
+        <v>132</v>
       </c>
       <c r="F148" t="s">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="G148" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>39</v>
       </c>
@@ -5848,22 +5849,22 @@
         <v>108</v>
       </c>
       <c r="C149" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D149">
-        <v>15</v>
-      </c>
-      <c r="E149">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="E149" t="s">
+        <v>132</v>
       </c>
       <c r="F149" t="s">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="G149" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>39</v>
       </c>
@@ -5871,22 +5872,22 @@
         <v>108</v>
       </c>
       <c r="C150" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="D150">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="E150" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="F150" t="s">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="G150" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>39</v>
       </c>
@@ -5894,22 +5895,22 @@
         <v>108</v>
       </c>
       <c r="C151" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="D151">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E151" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F151" t="s">
-        <v>72</v>
+        <v>41</v>
       </c>
       <c r="G151" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>39</v>
       </c>
@@ -5917,22 +5918,22 @@
         <v>108</v>
       </c>
       <c r="C152" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="D152">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E152" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F152" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="G152" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>39</v>
       </c>
@@ -5940,22 +5941,22 @@
         <v>108</v>
       </c>
       <c r="C153" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D153">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E153">
-        <v>250000000</v>
+        <v>3</v>
       </c>
       <c r="F153" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G153" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>39</v>
       </c>
@@ -5963,22 +5964,22 @@
         <v>108</v>
       </c>
       <c r="C154" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D154">
-        <v>20</v>
-      </c>
-      <c r="E154">
-        <v>150000000</v>
+        <v>8</v>
+      </c>
+      <c r="E154" t="s">
+        <v>140</v>
       </c>
       <c r="F154" t="s">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="G154" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>39</v>
       </c>
@@ -5986,22 +5987,22 @@
         <v>108</v>
       </c>
       <c r="C155" t="s">
-        <v>89</v>
+        <v>58</v>
       </c>
       <c r="D155">
-        <v>21</v>
-      </c>
-      <c r="E155">
-        <v>13</v>
+        <v>9</v>
+      </c>
+      <c r="E155" t="s">
+        <v>127</v>
       </c>
       <c r="F155" t="s">
-        <v>91</v>
+        <v>43</v>
       </c>
       <c r="G155" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>39</v>
       </c>
@@ -6009,22 +6010,22 @@
         <v>108</v>
       </c>
       <c r="C156" t="s">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="D156">
-        <v>22</v>
-      </c>
-      <c r="E156">
-        <v>179</v>
+        <v>10</v>
+      </c>
+      <c r="E156" t="s">
+        <v>127</v>
       </c>
       <c r="F156" t="s">
-        <v>92</v>
+        <v>43</v>
       </c>
       <c r="G156" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>39</v>
       </c>
@@ -6032,298 +6033,298 @@
         <v>108</v>
       </c>
       <c r="C157" t="s">
-        <v>95</v>
+        <v>57</v>
       </c>
       <c r="D157">
-        <v>23</v>
-      </c>
-      <c r="E157">
-        <v>1</v>
+        <v>11</v>
+      </c>
+      <c r="E157" t="s">
+        <v>127</v>
       </c>
       <c r="F157" t="s">
-        <v>91</v>
+        <v>43</v>
       </c>
       <c r="G157" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>39</v>
       </c>
       <c r="B158" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C158" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="D158">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E158" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="F158" t="s">
         <v>43</v>
       </c>
       <c r="G158" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>39</v>
       </c>
       <c r="B159" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C159" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="D159">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="E159" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="F159" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G159" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>39</v>
       </c>
       <c r="B160" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C160" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="D160">
-        <v>2</v>
-      </c>
-      <c r="E160" t="s">
-        <v>132</v>
+        <v>14</v>
+      </c>
+      <c r="E160">
+        <v>13</v>
       </c>
       <c r="F160" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="G160" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>39</v>
       </c>
       <c r="B161" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C161" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D161">
-        <v>3</v>
-      </c>
-      <c r="E161" t="s">
-        <v>132</v>
+        <v>15</v>
+      </c>
+      <c r="E161">
+        <v>1</v>
       </c>
       <c r="F161" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="G161" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>39</v>
       </c>
       <c r="B162" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C162" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="D162">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="E162" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="F162" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="G162" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>39</v>
       </c>
       <c r="B163" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C163" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="D163">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E163" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F163" t="s">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="G163" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>39</v>
       </c>
       <c r="B164" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C164" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="D164">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E164" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F164" t="s">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="G164" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>39</v>
       </c>
       <c r="B165" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C165" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="D165">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E165">
-        <v>3</v>
+        <v>250000000</v>
       </c>
       <c r="F165" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G165" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>39</v>
       </c>
       <c r="B166" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C166" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D166">
-        <v>8</v>
-      </c>
-      <c r="E166" t="s">
-        <v>140</v>
+        <v>20</v>
+      </c>
+      <c r="E166">
+        <v>150000000</v>
       </c>
       <c r="F166" t="s">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="G166" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>39</v>
       </c>
       <c r="B167" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C167" t="s">
-        <v>58</v>
+        <v>89</v>
       </c>
       <c r="D167">
-        <v>9</v>
-      </c>
-      <c r="E167" t="s">
-        <v>127</v>
+        <v>21</v>
+      </c>
+      <c r="E167">
+        <v>13</v>
       </c>
       <c r="F167" t="s">
-        <v>43</v>
+        <v>91</v>
       </c>
       <c r="G167" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>39</v>
       </c>
       <c r="B168" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C168" t="s">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="D168">
-        <v>10</v>
-      </c>
-      <c r="E168" t="s">
-        <v>127</v>
+        <v>22</v>
+      </c>
+      <c r="E168">
+        <v>179</v>
       </c>
       <c r="F168" t="s">
-        <v>43</v>
+        <v>92</v>
       </c>
       <c r="G168" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>39</v>
       </c>
       <c r="B169" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C169" t="s">
-        <v>57</v>
+        <v>95</v>
       </c>
       <c r="D169">
-        <v>11</v>
-      </c>
-      <c r="E169" t="s">
-        <v>127</v>
+        <v>23</v>
+      </c>
+      <c r="E169">
+        <v>1</v>
       </c>
       <c r="F169" t="s">
-        <v>43</v>
+        <v>91</v>
       </c>
       <c r="G169" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>39</v>
       </c>
@@ -6331,22 +6332,22 @@
         <v>109</v>
       </c>
       <c r="C170" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="D170">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E170" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="F170" t="s">
         <v>43</v>
       </c>
       <c r="G170" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>39</v>
       </c>
@@ -6354,22 +6355,22 @@
         <v>109</v>
       </c>
       <c r="C171" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D171">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E171" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F171" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G171" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>39</v>
       </c>
@@ -6377,22 +6378,22 @@
         <v>109</v>
       </c>
       <c r="C172" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="D172">
-        <v>14</v>
-      </c>
-      <c r="E172">
-        <v>13</v>
+        <v>2</v>
+      </c>
+      <c r="E172" t="s">
+        <v>132</v>
       </c>
       <c r="F172" t="s">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="G172" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>39</v>
       </c>
@@ -6400,22 +6401,22 @@
         <v>109</v>
       </c>
       <c r="C173" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D173">
-        <v>15</v>
-      </c>
-      <c r="E173">
-        <v>13</v>
+        <v>3</v>
+      </c>
+      <c r="E173" t="s">
+        <v>132</v>
       </c>
       <c r="F173" t="s">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="G173" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>39</v>
       </c>
@@ -6423,22 +6424,22 @@
         <v>109</v>
       </c>
       <c r="C174" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="D174">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="E174" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="F174" t="s">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="G174" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>39</v>
       </c>
@@ -6446,22 +6447,22 @@
         <v>109</v>
       </c>
       <c r="C175" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="D175">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E175" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F175" t="s">
-        <v>72</v>
+        <v>41</v>
       </c>
       <c r="G175" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>39</v>
       </c>
@@ -6469,22 +6470,22 @@
         <v>109</v>
       </c>
       <c r="C176" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="D176">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E176" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F176" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="G176" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>39</v>
       </c>
@@ -6492,22 +6493,22 @@
         <v>109</v>
       </c>
       <c r="C177" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D177">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E177">
-        <v>250000000</v>
+        <v>3</v>
       </c>
       <c r="F177" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G177" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>39</v>
       </c>
@@ -6515,22 +6516,22 @@
         <v>109</v>
       </c>
       <c r="C178" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D178">
-        <v>20</v>
-      </c>
-      <c r="E178">
-        <v>150000000</v>
+        <v>8</v>
+      </c>
+      <c r="E178" t="s">
+        <v>140</v>
       </c>
       <c r="F178" t="s">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="G178" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>39</v>
       </c>
@@ -6538,22 +6539,22 @@
         <v>109</v>
       </c>
       <c r="C179" t="s">
-        <v>89</v>
+        <v>58</v>
       </c>
       <c r="D179">
-        <v>21</v>
-      </c>
-      <c r="E179">
-        <v>13</v>
+        <v>9</v>
+      </c>
+      <c r="E179" t="s">
+        <v>127</v>
       </c>
       <c r="F179" t="s">
-        <v>91</v>
+        <v>43</v>
       </c>
       <c r="G179" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>39</v>
       </c>
@@ -6561,22 +6562,22 @@
         <v>109</v>
       </c>
       <c r="C180" t="s">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="D180">
-        <v>22</v>
-      </c>
-      <c r="E180">
-        <v>179</v>
+        <v>10</v>
+      </c>
+      <c r="E180" t="s">
+        <v>127</v>
       </c>
       <c r="F180" t="s">
-        <v>92</v>
+        <v>43</v>
       </c>
       <c r="G180" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>39</v>
       </c>
@@ -6584,298 +6585,298 @@
         <v>109</v>
       </c>
       <c r="C181" t="s">
-        <v>95</v>
+        <v>57</v>
       </c>
       <c r="D181">
-        <v>23</v>
-      </c>
-      <c r="E181">
-        <v>1</v>
+        <v>11</v>
+      </c>
+      <c r="E181" t="s">
+        <v>127</v>
       </c>
       <c r="F181" t="s">
-        <v>91</v>
+        <v>43</v>
       </c>
       <c r="G181" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>39</v>
       </c>
       <c r="B182" t="s">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="C182" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="D182">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E182" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="F182" t="s">
         <v>43</v>
       </c>
       <c r="G182" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>39</v>
       </c>
       <c r="B183" t="s">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="C183" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="D183">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="E183" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="F183" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G183" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>39</v>
       </c>
       <c r="B184" t="s">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="C184" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="D184">
-        <v>2</v>
-      </c>
-      <c r="E184" t="s">
-        <v>132</v>
+        <v>14</v>
+      </c>
+      <c r="E184">
+        <v>13</v>
       </c>
       <c r="F184" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="G184" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>39</v>
       </c>
       <c r="B185" t="s">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="C185" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D185">
-        <v>3</v>
-      </c>
-      <c r="E185" t="s">
-        <v>132</v>
+        <v>15</v>
+      </c>
+      <c r="E185">
+        <v>13</v>
       </c>
       <c r="F185" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="G185" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>39</v>
       </c>
       <c r="B186" t="s">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="C186" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="D186">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="E186" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="F186" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="G186" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>39</v>
       </c>
       <c r="B187" t="s">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="C187" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="D187">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E187" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F187" t="s">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="G187" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>39</v>
       </c>
       <c r="B188" t="s">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="C188" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="D188">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E188" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F188" t="s">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="G188" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>39</v>
       </c>
       <c r="B189" t="s">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="C189" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="D189">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E189">
-        <v>3</v>
+        <v>250000000</v>
       </c>
       <c r="F189" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G189" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>39</v>
       </c>
       <c r="B190" t="s">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="C190" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D190">
-        <v>8</v>
-      </c>
-      <c r="E190" t="s">
-        <v>140</v>
+        <v>20</v>
+      </c>
+      <c r="E190">
+        <v>150000000</v>
       </c>
       <c r="F190" t="s">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="G190" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>39</v>
       </c>
       <c r="B191" t="s">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="C191" t="s">
-        <v>58</v>
+        <v>89</v>
       </c>
       <c r="D191">
-        <v>9</v>
-      </c>
-      <c r="E191" t="s">
-        <v>127</v>
+        <v>21</v>
+      </c>
+      <c r="E191">
+        <v>13</v>
       </c>
       <c r="F191" t="s">
-        <v>43</v>
+        <v>91</v>
       </c>
       <c r="G191" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>39</v>
       </c>
       <c r="B192" t="s">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="C192" t="s">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="D192">
-        <v>10</v>
-      </c>
-      <c r="E192" t="s">
-        <v>127</v>
+        <v>22</v>
+      </c>
+      <c r="E192">
+        <v>179</v>
       </c>
       <c r="F192" t="s">
-        <v>43</v>
+        <v>92</v>
       </c>
       <c r="G192" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>39</v>
       </c>
       <c r="B193" t="s">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="C193" t="s">
-        <v>57</v>
+        <v>95</v>
       </c>
       <c r="D193">
-        <v>11</v>
-      </c>
-      <c r="E193" t="s">
-        <v>127</v>
+        <v>23</v>
+      </c>
+      <c r="E193">
+        <v>1</v>
       </c>
       <c r="F193" t="s">
-        <v>43</v>
+        <v>91</v>
       </c>
       <c r="G193" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>39</v>
       </c>
@@ -6883,22 +6884,22 @@
         <v>129</v>
       </c>
       <c r="C194" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="D194">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E194" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="F194" t="s">
         <v>43</v>
       </c>
       <c r="G194" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="195" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>39</v>
       </c>
@@ -6906,22 +6907,22 @@
         <v>129</v>
       </c>
       <c r="C195" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D195">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E195" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F195" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G195" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>39</v>
       </c>
@@ -6929,22 +6930,22 @@
         <v>129</v>
       </c>
       <c r="C196" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="D196">
-        <v>14</v>
-      </c>
-      <c r="E196">
-        <v>13</v>
+        <v>2</v>
+      </c>
+      <c r="E196" t="s">
+        <v>132</v>
       </c>
       <c r="F196" t="s">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="G196" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="197" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>39</v>
       </c>
@@ -6952,22 +6953,22 @@
         <v>129</v>
       </c>
       <c r="C197" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D197">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="E197" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="F197" t="s">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="G197" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>39</v>
       </c>
@@ -6975,22 +6976,22 @@
         <v>129</v>
       </c>
       <c r="C198" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="D198">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="E198" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="F198" t="s">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="G198" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="199" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>39</v>
       </c>
@@ -6998,22 +6999,22 @@
         <v>129</v>
       </c>
       <c r="C199" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="D199">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E199" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F199" t="s">
-        <v>72</v>
+        <v>41</v>
       </c>
       <c r="G199" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>39</v>
       </c>
@@ -7021,22 +7022,22 @@
         <v>129</v>
       </c>
       <c r="C200" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="D200">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E200" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F200" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="G200" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>39</v>
       </c>
@@ -7044,22 +7045,22 @@
         <v>129</v>
       </c>
       <c r="C201" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D201">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E201">
-        <v>250000000</v>
+        <v>3</v>
       </c>
       <c r="F201" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G201" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="202" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>39</v>
       </c>
@@ -7067,22 +7068,22 @@
         <v>129</v>
       </c>
       <c r="C202" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D202">
-        <v>20</v>
-      </c>
-      <c r="E202">
-        <v>150000000</v>
+        <v>8</v>
+      </c>
+      <c r="E202" t="s">
+        <v>140</v>
       </c>
       <c r="F202" t="s">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="G202" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="203" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>39</v>
       </c>
@@ -7090,22 +7091,22 @@
         <v>129</v>
       </c>
       <c r="C203" t="s">
-        <v>89</v>
+        <v>58</v>
       </c>
       <c r="D203">
-        <v>21</v>
-      </c>
-      <c r="E203">
-        <v>13</v>
+        <v>9</v>
+      </c>
+      <c r="E203" t="s">
+        <v>127</v>
       </c>
       <c r="F203" t="s">
-        <v>91</v>
+        <v>43</v>
       </c>
       <c r="G203" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="204" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>39</v>
       </c>
@@ -7113,22 +7114,22 @@
         <v>129</v>
       </c>
       <c r="C204" t="s">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="D204">
-        <v>22</v>
-      </c>
-      <c r="E204">
-        <v>179</v>
+        <v>10</v>
+      </c>
+      <c r="E204" t="s">
+        <v>127</v>
       </c>
       <c r="F204" t="s">
-        <v>92</v>
+        <v>43</v>
       </c>
       <c r="G204" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="205" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>39</v>
       </c>
@@ -7136,26 +7137,309 @@
         <v>129</v>
       </c>
       <c r="C205" t="s">
+        <v>57</v>
+      </c>
+      <c r="D205">
+        <v>11</v>
+      </c>
+      <c r="E205" t="s">
+        <v>127</v>
+      </c>
+      <c r="F205" t="s">
+        <v>43</v>
+      </c>
+      <c r="G205" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="206" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>39</v>
+      </c>
+      <c r="B206" t="s">
+        <v>129</v>
+      </c>
+      <c r="C206" t="s">
+        <v>40</v>
+      </c>
+      <c r="D206">
+        <v>12</v>
+      </c>
+      <c r="E206" t="s">
+        <v>133</v>
+      </c>
+      <c r="F206" t="s">
+        <v>43</v>
+      </c>
+      <c r="G206" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="207" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>39</v>
+      </c>
+      <c r="B207" t="s">
+        <v>129</v>
+      </c>
+      <c r="C207" t="s">
+        <v>70</v>
+      </c>
+      <c r="D207">
+        <v>13</v>
+      </c>
+      <c r="E207" t="s">
+        <v>134</v>
+      </c>
+      <c r="F207" t="s">
+        <v>44</v>
+      </c>
+      <c r="G207" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="208" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>39</v>
+      </c>
+      <c r="B208" t="s">
+        <v>129</v>
+      </c>
+      <c r="C208" t="s">
+        <v>45</v>
+      </c>
+      <c r="D208">
+        <v>14</v>
+      </c>
+      <c r="E208">
+        <v>13</v>
+      </c>
+      <c r="F208" t="s">
+        <v>72</v>
+      </c>
+      <c r="G208" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="209" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>39</v>
+      </c>
+      <c r="B209" t="s">
+        <v>129</v>
+      </c>
+      <c r="C209" t="s">
+        <v>53</v>
+      </c>
+      <c r="D209">
+        <v>15</v>
+      </c>
+      <c r="E209" t="s">
+        <v>141</v>
+      </c>
+      <c r="F209" t="s">
+        <v>72</v>
+      </c>
+      <c r="G209" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="210" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>39</v>
+      </c>
+      <c r="B210" t="s">
+        <v>129</v>
+      </c>
+      <c r="C210" t="s">
+        <v>47</v>
+      </c>
+      <c r="D210">
+        <v>16</v>
+      </c>
+      <c r="E210" t="s">
+        <v>135</v>
+      </c>
+      <c r="F210" t="s">
+        <v>72</v>
+      </c>
+      <c r="G210" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="211" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>39</v>
+      </c>
+      <c r="B211" t="s">
+        <v>129</v>
+      </c>
+      <c r="C211" t="s">
+        <v>48</v>
+      </c>
+      <c r="D211">
+        <v>17</v>
+      </c>
+      <c r="E211" t="s">
+        <v>136</v>
+      </c>
+      <c r="F211" t="s">
+        <v>72</v>
+      </c>
+      <c r="G211" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="212" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>39</v>
+      </c>
+      <c r="B212" t="s">
+        <v>129</v>
+      </c>
+      <c r="C212" t="s">
+        <v>49</v>
+      </c>
+      <c r="D212">
+        <v>18</v>
+      </c>
+      <c r="E212" t="s">
+        <v>137</v>
+      </c>
+      <c r="F212" t="s">
+        <v>72</v>
+      </c>
+      <c r="G212" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="213" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>39</v>
+      </c>
+      <c r="B213" t="s">
+        <v>129</v>
+      </c>
+      <c r="C213" t="s">
+        <v>68</v>
+      </c>
+      <c r="D213">
+        <v>19</v>
+      </c>
+      <c r="E213">
+        <v>250000000</v>
+      </c>
+      <c r="F213" t="s">
+        <v>73</v>
+      </c>
+      <c r="G213" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="214" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>39</v>
+      </c>
+      <c r="B214" t="s">
+        <v>129</v>
+      </c>
+      <c r="C214" t="s">
+        <v>69</v>
+      </c>
+      <c r="D214">
+        <v>20</v>
+      </c>
+      <c r="E214">
+        <v>150000000</v>
+      </c>
+      <c r="F214" t="s">
+        <v>73</v>
+      </c>
+      <c r="G214" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="215" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>39</v>
+      </c>
+      <c r="B215" t="s">
+        <v>129</v>
+      </c>
+      <c r="C215" t="s">
+        <v>89</v>
+      </c>
+      <c r="D215">
+        <v>21</v>
+      </c>
+      <c r="E215">
+        <v>13</v>
+      </c>
+      <c r="F215" t="s">
+        <v>91</v>
+      </c>
+      <c r="G215" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="216" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>39</v>
+      </c>
+      <c r="B216" t="s">
+        <v>129</v>
+      </c>
+      <c r="C216" t="s">
+        <v>90</v>
+      </c>
+      <c r="D216">
+        <v>22</v>
+      </c>
+      <c r="E216">
+        <v>179</v>
+      </c>
+      <c r="F216" t="s">
+        <v>92</v>
+      </c>
+      <c r="G216" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="217" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>39</v>
+      </c>
+      <c r="B217" t="s">
+        <v>129</v>
+      </c>
+      <c r="C217" t="s">
         <v>95</v>
       </c>
-      <c r="D205">
+      <c r="D217">
         <v>23</v>
       </c>
-      <c r="E205">
-        <v>1</v>
-      </c>
-      <c r="F205" t="s">
+      <c r="E217">
+        <v>1</v>
+      </c>
+      <c r="F217" t="s">
         <v>91</v>
       </c>
-      <c r="G205" t="s">
+      <c r="G217" t="s">
         <v>96</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H297">
-    <sortCondition ref="A2:A297"/>
-    <sortCondition ref="B2:B297"/>
-    <sortCondition ref="D2:D297"/>
+  <autoFilter ref="A1:G217" xr:uid="{9375A35C-8A58-4D70-9436-2E641DE51D25}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="FOAK Baseline Well Executed"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H309">
+    <sortCondition ref="A2:A309"/>
+    <sortCondition ref="B2:B309"/>
+    <sortCondition ref="D2:D309"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="90" verticalDpi="90" r:id="rId1"/>
@@ -7178,6 +7462,9 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>13</v>
+      </c>
       <c r="B1" t="s">
         <v>110</v>
       </c>
@@ -7758,7 +8045,7 @@
         <v>107</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -7780,7 +8067,7 @@
         <v>87</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -7791,7 +8078,7 @@
         <v>106</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -7802,7 +8089,7 @@
         <v>105</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -7824,7 +8111,7 @@
         <v>109</v>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -7835,7 +8122,7 @@
         <v>129</v>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/src/technology/small-modular-reactor/small-modular-reactor.xlsx
+++ b/src/technology/small-modular-reactor/small-modular-reactor.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rhanes\GitHub\tyche\src\technology\small-modular-reactor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D019919-EF52-4B91-97A0-3761398A9FC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C171F87-7AA2-4827-8500-3B3619B00F61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1875" yWindow="1620" windowWidth="25185" windowHeight="17685" tabRatio="778" activeTab="4" xr2:uid="{277ED3FD-2B20-4A36-BB03-16AF83BDC75C}"/>
+    <workbookView xWindow="28050" yWindow="840" windowWidth="22965" windowHeight="19200" tabRatio="778" activeTab="4" xr2:uid="{277ED3FD-2B20-4A36-BB03-16AF83BDC75C}"/>
   </bookViews>
   <sheets>
     <sheet name="indices" sheetId="1" r:id="rId1"/>
@@ -2423,7 +2423,6 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9375A35C-8A58-4D70-9436-2E641DE51D25}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:G217"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3012,7 +3011,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>39</v>
       </c>
@@ -3035,7 +3034,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>39</v>
       </c>
@@ -3058,7 +3057,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>39</v>
       </c>
@@ -3081,7 +3080,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>39</v>
       </c>
@@ -3104,7 +3103,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>39</v>
       </c>
@@ -3127,7 +3126,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>39</v>
       </c>
@@ -3150,7 +3149,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>39</v>
       </c>
@@ -3173,7 +3172,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>39</v>
       </c>
@@ -3196,7 +3195,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>39</v>
       </c>
@@ -3219,7 +3218,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>39</v>
       </c>
@@ -3242,7 +3241,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>39</v>
       </c>
@@ -3265,7 +3264,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="37" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>39</v>
       </c>
@@ -3288,7 +3287,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="38" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>39</v>
       </c>
@@ -3311,7 +3310,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>39</v>
       </c>
@@ -3334,7 +3333,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="40" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>39</v>
       </c>
@@ -3357,7 +3356,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="41" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>39</v>
       </c>
@@ -3380,7 +3379,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="42" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>39</v>
       </c>
@@ -3403,7 +3402,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="43" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>39</v>
       </c>
@@ -3426,7 +3425,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="44" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>39</v>
       </c>
@@ -3449,7 +3448,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="45" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>39</v>
       </c>
@@ -3472,7 +3471,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="46" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>39</v>
       </c>
@@ -3495,7 +3494,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="47" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>39</v>
       </c>
@@ -3518,7 +3517,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="48" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>39</v>
       </c>
@@ -3541,7 +3540,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="49" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>39</v>
       </c>
@@ -3564,7 +3563,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="50" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>39</v>
       </c>
@@ -3587,7 +3586,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="51" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>39</v>
       </c>
@@ -3610,7 +3609,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="52" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>39</v>
       </c>
@@ -3633,7 +3632,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="53" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>39</v>
       </c>
@@ -3656,7 +3655,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="54" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>39</v>
       </c>
@@ -3679,7 +3678,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="55" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>39</v>
       </c>
@@ -3702,7 +3701,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="56" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>39</v>
       </c>
@@ -3725,7 +3724,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="57" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>39</v>
       </c>
@@ -3748,7 +3747,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="58" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>39</v>
       </c>
@@ -3771,7 +3770,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="59" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>39</v>
       </c>
@@ -3794,7 +3793,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="60" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>39</v>
       </c>
@@ -3817,7 +3816,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="61" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>39</v>
       </c>
@@ -3840,7 +3839,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="62" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>39</v>
       </c>
@@ -3863,7 +3862,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="63" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>39</v>
       </c>
@@ -3886,7 +3885,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="64" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>39</v>
       </c>
@@ -3909,7 +3908,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="65" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>39</v>
       </c>
@@ -3932,7 +3931,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="66" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>39</v>
       </c>
@@ -3955,7 +3954,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="67" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>39</v>
       </c>
@@ -3978,7 +3977,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="68" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>39</v>
       </c>
@@ -4001,7 +4000,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="69" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>39</v>
       </c>
@@ -4024,7 +4023,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="70" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>39</v>
       </c>
@@ -4047,7 +4046,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="71" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>39</v>
       </c>
@@ -4070,7 +4069,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="72" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>39</v>
       </c>
@@ -4093,7 +4092,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="73" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>39</v>
       </c>
@@ -4116,7 +4115,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="74" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>39</v>
       </c>
@@ -4139,7 +4138,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="75" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>39</v>
       </c>
@@ -4162,7 +4161,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="76" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>39</v>
       </c>
@@ -4185,7 +4184,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="77" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>39</v>
       </c>
@@ -4208,7 +4207,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="78" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>39</v>
       </c>
@@ -4231,7 +4230,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="79" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>39</v>
       </c>
@@ -4254,7 +4253,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="80" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>39</v>
       </c>
@@ -4277,7 +4276,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="81" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>39</v>
       </c>
@@ -4300,7 +4299,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="82" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>39</v>
       </c>
@@ -4323,7 +4322,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="83" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>39</v>
       </c>
@@ -4346,7 +4345,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="84" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>39</v>
       </c>
@@ -4369,7 +4368,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="85" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>39</v>
       </c>
@@ -4392,7 +4391,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="86" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>39</v>
       </c>
@@ -4415,7 +4414,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="87" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>39</v>
       </c>
@@ -4438,7 +4437,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="88" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>39</v>
       </c>
@@ -4461,7 +4460,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="89" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>39</v>
       </c>
@@ -4484,7 +4483,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="90" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>39</v>
       </c>
@@ -4507,7 +4506,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="91" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>39</v>
       </c>
@@ -4530,7 +4529,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="92" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>39</v>
       </c>
@@ -4553,7 +4552,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="93" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>39</v>
       </c>
@@ -4576,7 +4575,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="94" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>39</v>
       </c>
@@ -4599,7 +4598,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="95" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>39</v>
       </c>
@@ -4622,7 +4621,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="96" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>39</v>
       </c>
@@ -4645,7 +4644,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="97" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>39</v>
       </c>
@@ -4668,7 +4667,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="98" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>39</v>
       </c>
@@ -4691,7 +4690,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="99" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>39</v>
       </c>
@@ -4714,7 +4713,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="100" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>39</v>
       </c>
@@ -4737,7 +4736,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="101" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>39</v>
       </c>
@@ -4760,7 +4759,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="102" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>39</v>
       </c>
@@ -4783,7 +4782,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="103" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>39</v>
       </c>
@@ -4806,7 +4805,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="104" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>39</v>
       </c>
@@ -4829,7 +4828,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="105" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>39</v>
       </c>
@@ -4852,7 +4851,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="106" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>39</v>
       </c>
@@ -4875,7 +4874,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="107" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>39</v>
       </c>
@@ -4898,7 +4897,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="108" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>39</v>
       </c>
@@ -4921,7 +4920,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="109" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>39</v>
       </c>
@@ -4944,7 +4943,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="110" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>39</v>
       </c>
@@ -4967,7 +4966,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="111" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>39</v>
       </c>
@@ -4990,7 +4989,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="112" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>39</v>
       </c>
@@ -5013,7 +5012,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="113" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>39</v>
       </c>
@@ -5036,7 +5035,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="114" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>39</v>
       </c>
@@ -5059,7 +5058,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="115" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>39</v>
       </c>
@@ -5082,7 +5081,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="116" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>39</v>
       </c>
@@ -5105,7 +5104,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="117" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>39</v>
       </c>
@@ -5128,7 +5127,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="118" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>39</v>
       </c>
@@ -5151,7 +5150,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="119" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>39</v>
       </c>
@@ -5174,7 +5173,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="120" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>39</v>
       </c>
@@ -5197,7 +5196,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="121" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>39</v>
       </c>
@@ -5220,7 +5219,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="122" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>39</v>
       </c>
@@ -5243,7 +5242,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="123" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>39</v>
       </c>
@@ -5266,7 +5265,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="124" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>39</v>
       </c>
@@ -5289,7 +5288,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="125" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>39</v>
       </c>
@@ -5312,7 +5311,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="126" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>39</v>
       </c>
@@ -5335,7 +5334,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="127" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>39</v>
       </c>
@@ -5358,7 +5357,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="128" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>39</v>
       </c>
@@ -5381,7 +5380,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="129" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>39</v>
       </c>
@@ -5404,7 +5403,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="130" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>39</v>
       </c>
@@ -5427,7 +5426,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="131" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>39</v>
       </c>
@@ -5450,7 +5449,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="132" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>39</v>
       </c>
@@ -5473,7 +5472,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="133" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>39</v>
       </c>
@@ -5496,7 +5495,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="134" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>39</v>
       </c>
@@ -5519,7 +5518,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="135" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>39</v>
       </c>
@@ -5542,7 +5541,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="136" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>39</v>
       </c>
@@ -5565,7 +5564,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="137" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>39</v>
       </c>
@@ -5588,7 +5587,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="138" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>39</v>
       </c>
@@ -5611,7 +5610,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="139" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>39</v>
       </c>
@@ -5634,7 +5633,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="140" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>39</v>
       </c>
@@ -5657,7 +5656,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="141" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>39</v>
       </c>
@@ -5680,7 +5679,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="142" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>39</v>
       </c>
@@ -5703,7 +5702,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="143" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>39</v>
       </c>
@@ -5726,7 +5725,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="144" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>39</v>
       </c>
@@ -5749,7 +5748,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="145" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>39</v>
       </c>
@@ -5772,7 +5771,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="146" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>39</v>
       </c>
@@ -5795,7 +5794,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="147" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>39</v>
       </c>
@@ -5818,7 +5817,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="148" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>39</v>
       </c>
@@ -5841,7 +5840,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="149" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>39</v>
       </c>
@@ -5864,7 +5863,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="150" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>39</v>
       </c>
@@ -5887,7 +5886,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="151" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>39</v>
       </c>
@@ -5910,7 +5909,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="152" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>39</v>
       </c>
@@ -5933,7 +5932,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="153" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>39</v>
       </c>
@@ -5956,7 +5955,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="154" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>39</v>
       </c>
@@ -5979,7 +5978,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="155" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>39</v>
       </c>
@@ -6002,7 +6001,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="156" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>39</v>
       </c>
@@ -6025,7 +6024,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="157" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>39</v>
       </c>
@@ -6048,7 +6047,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="158" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>39</v>
       </c>
@@ -6071,7 +6070,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="159" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>39</v>
       </c>
@@ -6094,7 +6093,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="160" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>39</v>
       </c>
@@ -6117,7 +6116,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="161" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>39</v>
       </c>
@@ -6140,7 +6139,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="162" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>39</v>
       </c>
@@ -6163,7 +6162,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="163" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>39</v>
       </c>
@@ -6186,7 +6185,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="164" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>39</v>
       </c>
@@ -6209,7 +6208,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="165" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>39</v>
       </c>
@@ -6232,7 +6231,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="166" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>39</v>
       </c>
@@ -6255,7 +6254,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="167" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>39</v>
       </c>
@@ -6278,7 +6277,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="168" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>39</v>
       </c>
@@ -6301,7 +6300,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="169" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>39</v>
       </c>
@@ -6324,7 +6323,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="170" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>39</v>
       </c>
@@ -6347,7 +6346,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="171" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>39</v>
       </c>
@@ -6370,7 +6369,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="172" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>39</v>
       </c>
@@ -6393,7 +6392,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="173" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>39</v>
       </c>
@@ -6416,7 +6415,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="174" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>39</v>
       </c>
@@ -6439,7 +6438,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="175" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>39</v>
       </c>
@@ -6462,7 +6461,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="176" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>39</v>
       </c>
@@ -6485,7 +6484,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="177" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>39</v>
       </c>
@@ -6508,7 +6507,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="178" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>39</v>
       </c>
@@ -6531,7 +6530,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="179" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>39</v>
       </c>
@@ -6554,7 +6553,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="180" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>39</v>
       </c>
@@ -6577,7 +6576,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="181" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>39</v>
       </c>
@@ -6600,7 +6599,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="182" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>39</v>
       </c>
@@ -6623,7 +6622,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="183" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>39</v>
       </c>
@@ -6646,7 +6645,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="184" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>39</v>
       </c>
@@ -6669,7 +6668,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="185" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>39</v>
       </c>
@@ -6692,7 +6691,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="186" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>39</v>
       </c>
@@ -6715,7 +6714,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="187" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>39</v>
       </c>
@@ -6738,7 +6737,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="188" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>39</v>
       </c>
@@ -6761,7 +6760,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="189" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>39</v>
       </c>
@@ -6784,7 +6783,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="190" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>39</v>
       </c>
@@ -6807,7 +6806,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="191" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>39</v>
       </c>
@@ -6830,7 +6829,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="192" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>39</v>
       </c>
@@ -6853,7 +6852,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="193" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>39</v>
       </c>
@@ -6876,7 +6875,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="194" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>39</v>
       </c>
@@ -6899,7 +6898,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="195" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>39</v>
       </c>
@@ -6922,7 +6921,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="196" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>39</v>
       </c>
@@ -6945,7 +6944,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="197" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>39</v>
       </c>
@@ -6968,7 +6967,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="198" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>39</v>
       </c>
@@ -6991,7 +6990,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="199" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>39</v>
       </c>
@@ -7014,7 +7013,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="200" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>39</v>
       </c>
@@ -7037,7 +7036,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="201" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>39</v>
       </c>
@@ -7060,7 +7059,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="202" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>39</v>
       </c>
@@ -7083,7 +7082,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="203" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>39</v>
       </c>
@@ -7106,7 +7105,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="204" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>39</v>
       </c>
@@ -7129,7 +7128,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="205" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>39</v>
       </c>
@@ -7152,7 +7151,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="206" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>39</v>
       </c>
@@ -7175,7 +7174,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="207" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>39</v>
       </c>
@@ -7198,7 +7197,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="208" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>39</v>
       </c>
@@ -7221,7 +7220,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="209" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>39</v>
       </c>
@@ -7244,7 +7243,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="210" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>39</v>
       </c>
@@ -7267,7 +7266,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="211" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>39</v>
       </c>
@@ -7290,7 +7289,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="212" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>39</v>
       </c>
@@ -7313,7 +7312,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="213" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>39</v>
       </c>
@@ -7336,7 +7335,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="214" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>39</v>
       </c>
@@ -7359,7 +7358,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="215" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>39</v>
       </c>
@@ -7382,7 +7381,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="216" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>39</v>
       </c>
@@ -7405,7 +7404,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="217" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>39</v>
       </c>
@@ -7429,13 +7428,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G217" xr:uid="{9375A35C-8A58-4D70-9436-2E641DE51D25}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="FOAK Baseline Well Executed"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H309">
     <sortCondition ref="A2:A309"/>
     <sortCondition ref="B2:B309"/>

--- a/src/technology/small-modular-reactor/small-modular-reactor.xlsx
+++ b/src/technology/small-modular-reactor/small-modular-reactor.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rhanes\GitHub\tyche\src\technology\small-modular-reactor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C171F87-7AA2-4827-8500-3B3619B00F61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4186DD4-F1DD-481B-806C-67F943E7250B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28050" yWindow="840" windowWidth="22965" windowHeight="19200" tabRatio="778" activeTab="4" xr2:uid="{277ED3FD-2B20-4A36-BB03-16AF83BDC75C}"/>
+    <workbookView xWindow="23730" yWindow="1155" windowWidth="27600" windowHeight="19515" tabRatio="778" activeTab="4" xr2:uid="{277ED3FD-2B20-4A36-BB03-16AF83BDC75C}"/>
   </bookViews>
   <sheets>
     <sheet name="indices" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">designs!$A$1:$G$911</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">indices!$A$1:$F$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">indices!$A$1:$F$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">parameters!$A$1:$G$217</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1613" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1625" uniqueCount="152">
   <si>
     <t>Category</t>
   </si>
@@ -496,6 +496,15 @@
   </si>
   <si>
     <t>Ranges</t>
+  </si>
+  <si>
+    <t>USD/kWe</t>
+  </si>
+  <si>
+    <t>MWh/year</t>
+  </si>
+  <si>
+    <t>Total OCC</t>
   </si>
 </sst>
 </file>
@@ -847,7 +856,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AF3D170-DEC1-4938-B961-67DBF048922E}">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.42578125" bestFit="1" customWidth="1"/>
@@ -953,20 +962,34 @@
         <v>39</v>
       </c>
       <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" t="s">
+        <v>151</v>
+      </c>
+      <c r="D7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" t="s">
         <v>11</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C8" t="s">
         <v>100</v>
       </c>
-      <c r="D7">
+      <c r="D8">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:F24">
-    <sortCondition ref="A3:A24"/>
-    <sortCondition ref="B3:B24"/>
-    <sortCondition ref="D3:D24"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:F25">
+    <sortCondition ref="A3:A25"/>
+    <sortCondition ref="B3:B25"/>
+    <sortCondition ref="D3:D25"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -7908,7 +7931,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08421A62-7A7F-4754-940E-DE21752714F2}">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
@@ -7943,6 +7966,9 @@
       <c r="C2" t="s">
         <v>28</v>
       </c>
+      <c r="D2" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
@@ -7954,6 +7980,9 @@
       <c r="C3" t="s">
         <v>100</v>
       </c>
+      <c r="D3" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
@@ -7965,6 +7994,9 @@
       <c r="C4" t="s">
         <v>101</v>
       </c>
+      <c r="D4" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
@@ -7976,6 +8008,9 @@
       <c r="C5" t="s">
         <v>102</v>
       </c>
+      <c r="D5" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
@@ -7986,6 +8021,23 @@
       </c>
       <c r="C6" t="s">
         <v>103</v>
+      </c>
+      <c r="D6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" t="s">
+        <v>151</v>
+      </c>
+      <c r="D7" t="s">
+        <v>73</v>
       </c>
     </row>
   </sheetData>

--- a/src/technology/small-modular-reactor/small-modular-reactor.xlsx
+++ b/src/technology/small-modular-reactor/small-modular-reactor.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rhanes\GitHub\tyche\src\technology\small-modular-reactor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4186DD4-F1DD-481B-806C-67F943E7250B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8CC9164-BF00-4468-834E-1AB2E91DAE27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23730" yWindow="1155" windowWidth="27600" windowHeight="19515" tabRatio="778" activeTab="4" xr2:uid="{277ED3FD-2B20-4A36-BB03-16AF83BDC75C}"/>
+    <workbookView xWindow="20610" yWindow="975" windowWidth="28185" windowHeight="19515" tabRatio="778" activeTab="4" xr2:uid="{277ED3FD-2B20-4A36-BB03-16AF83BDC75C}"/>
   </bookViews>
   <sheets>
     <sheet name="indices" sheetId="1" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1625" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1624" uniqueCount="152">
   <si>
     <t>Category</t>
   </si>
@@ -2453,7 +2453,7 @@
     <col min="2" max="2" width="27.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27.7109375" customWidth="1"/>
     <col min="4" max="4" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="50.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="58.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.42578125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="81.42578125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6.28515625" bestFit="1" customWidth="1"/>
@@ -7073,7 +7073,7 @@
         <v>7</v>
       </c>
       <c r="E201">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F201" t="s">
         <v>72</v>
@@ -7234,7 +7234,7 @@
         <v>14</v>
       </c>
       <c r="E208">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F208" t="s">
         <v>72</v>
@@ -7256,8 +7256,8 @@
       <c r="D209">
         <v>15</v>
       </c>
-      <c r="E209" t="s">
-        <v>141</v>
+      <c r="E209">
+        <v>6</v>
       </c>
       <c r="F209" t="s">
         <v>72</v>

--- a/src/technology/small-modular-reactor/small-modular-reactor.xlsx
+++ b/src/technology/small-modular-reactor/small-modular-reactor.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rhanes\GitHub\tyche\src\technology\small-modular-reactor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6256B30-DDC7-4616-A1D4-DC7E29F1FD88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F58FF924-531A-460B-8931-79D14348CE7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2130" yWindow="465" windowWidth="31920" windowHeight="20805" tabRatio="778" activeTab="6" xr2:uid="{277ED3FD-2B20-4A36-BB03-16AF83BDC75C}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="13125" windowHeight="18270" tabRatio="778" activeTab="4" xr2:uid="{277ED3FD-2B20-4A36-BB03-16AF83BDC75C}"/>
   </bookViews>
   <sheets>
     <sheet name="indices" sheetId="1" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2452" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2464" uniqueCount="159">
   <si>
     <t>Category</t>
   </si>
@@ -520,6 +520,12 @@
   </si>
   <si>
     <t>BOAK 3 of 6 Orders</t>
+  </si>
+  <si>
+    <t>Variable Op and Maint</t>
+  </si>
+  <si>
+    <t>Fixed Op and Maint</t>
   </si>
 </sst>
 </file>
@@ -871,7 +877,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AF3D170-DEC1-4938-B961-67DBF048922E}">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.42578125" bestFit="1" customWidth="1"/>
@@ -991,12 +997,40 @@
         <v>39</v>
       </c>
       <c r="B8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" t="s">
+        <v>157</v>
+      </c>
+      <c r="D8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" t="s">
+        <v>158</v>
+      </c>
+      <c r="D9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" t="s">
         <v>11</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C10" t="s">
         <v>97</v>
       </c>
-      <c r="D8">
+      <c r="D10">
         <v>0</v>
       </c>
     </row>
@@ -3542,7 +3576,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>39</v>
       </c>
@@ -3565,7 +3599,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>39</v>
       </c>
@@ -4094,7 +4128,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="47" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>39</v>
       </c>
@@ -4117,7 +4151,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="48" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>39</v>
       </c>
@@ -4163,7 +4197,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>39</v>
       </c>
@@ -4186,7 +4220,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>39</v>
       </c>
@@ -4209,7 +4243,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>39</v>
       </c>
@@ -4232,7 +4266,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>39</v>
       </c>
@@ -4255,7 +4289,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>39</v>
       </c>
@@ -4278,7 +4312,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>39</v>
       </c>
@@ -4301,7 +4335,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>39</v>
       </c>
@@ -4324,7 +4358,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>39</v>
       </c>
@@ -4347,7 +4381,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>39</v>
       </c>
@@ -4370,7 +4404,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>39</v>
       </c>
@@ -4393,7 +4427,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>39</v>
       </c>
@@ -4416,7 +4450,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>39</v>
       </c>
@@ -4439,7 +4473,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>39</v>
       </c>
@@ -4462,7 +4496,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>39</v>
       </c>
@@ -4485,7 +4519,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>39</v>
       </c>
@@ -4508,7 +4542,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>39</v>
       </c>
@@ -4531,7 +4565,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>39</v>
       </c>
@@ -4554,7 +4588,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>39</v>
       </c>
@@ -4577,7 +4611,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>39</v>
       </c>
@@ -4600,7 +4634,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>39</v>
       </c>
@@ -4623,7 +4657,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>39</v>
       </c>
@@ -4692,7 +4726,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>39</v>
       </c>
@@ -5198,7 +5232,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="95" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>39</v>
       </c>
@@ -5221,7 +5255,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="96" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>39</v>
       </c>
@@ -5750,7 +5784,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="119" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>39</v>
       </c>
@@ -5773,7 +5807,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="120" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>39</v>
       </c>
@@ -6302,7 +6336,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="143" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>39</v>
       </c>
@@ -6325,7 +6359,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="144" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>39</v>
       </c>
@@ -6854,7 +6888,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="167" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>39</v>
       </c>
@@ -6877,7 +6911,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="168" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>39</v>
       </c>
@@ -7406,7 +7440,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="191" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>39</v>
       </c>
@@ -7429,7 +7463,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="192" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>39</v>
       </c>
@@ -7958,7 +7992,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="215" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>39</v>
       </c>
@@ -7981,7 +8015,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="216" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>39</v>
       </c>
@@ -8027,7 +8061,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>39</v>
       </c>
@@ -8050,7 +8084,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>39</v>
       </c>
@@ -8073,7 +8107,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>39</v>
       </c>
@@ -8096,7 +8130,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>39</v>
       </c>
@@ -8119,7 +8153,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>39</v>
       </c>
@@ -8142,7 +8176,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>39</v>
       </c>
@@ -8165,7 +8199,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>39</v>
       </c>
@@ -8188,7 +8222,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>39</v>
       </c>
@@ -8211,7 +8245,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>39</v>
       </c>
@@ -8234,7 +8268,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>39</v>
       </c>
@@ -8257,7 +8291,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>39</v>
       </c>
@@ -8280,7 +8314,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>39</v>
       </c>
@@ -8303,7 +8337,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>39</v>
       </c>
@@ -8326,7 +8360,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>39</v>
       </c>
@@ -8349,7 +8383,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>39</v>
       </c>
@@ -8372,7 +8406,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>39</v>
       </c>
@@ -8395,7 +8429,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>39</v>
       </c>
@@ -8418,7 +8452,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>39</v>
       </c>
@@ -8441,7 +8475,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>39</v>
       </c>
@@ -8464,7 +8498,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>39</v>
       </c>
@@ -8487,7 +8521,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>39</v>
       </c>
@@ -8556,7 +8590,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>39</v>
       </c>
@@ -8579,7 +8613,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>39</v>
       </c>
@@ -8602,7 +8636,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>39</v>
       </c>
@@ -8625,7 +8659,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>39</v>
       </c>
@@ -8648,7 +8682,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>39</v>
       </c>
@@ -8671,7 +8705,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>39</v>
       </c>
@@ -8694,7 +8728,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>39</v>
       </c>
@@ -8717,7 +8751,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>39</v>
       </c>
@@ -8740,7 +8774,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>39</v>
       </c>
@@ -8763,7 +8797,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>39</v>
       </c>
@@ -8786,7 +8820,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>39</v>
       </c>
@@ -8809,7 +8843,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>39</v>
       </c>
@@ -8832,7 +8866,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>39</v>
       </c>
@@ -8855,7 +8889,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>39</v>
       </c>
@@ -8878,7 +8912,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>39</v>
       </c>
@@ -8901,7 +8935,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>39</v>
       </c>
@@ -8924,7 +8958,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>39</v>
       </c>
@@ -8947,7 +8981,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>39</v>
       </c>
@@ -8970,7 +9004,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>39</v>
       </c>
@@ -8993,7 +9027,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>39</v>
       </c>
@@ -9016,7 +9050,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>39</v>
       </c>
@@ -9039,7 +9073,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>39</v>
       </c>
@@ -9108,7 +9142,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>39</v>
       </c>
@@ -9131,7 +9165,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>39</v>
       </c>
@@ -9154,7 +9188,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>39</v>
       </c>
@@ -9177,7 +9211,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>39</v>
       </c>
@@ -9200,7 +9234,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>39</v>
       </c>
@@ -9223,7 +9257,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>39</v>
       </c>
@@ -9246,7 +9280,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="271" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>39</v>
       </c>
@@ -9269,7 +9303,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="272" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>39</v>
       </c>
@@ -9292,7 +9326,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>39</v>
       </c>
@@ -9315,7 +9349,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="274" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>39</v>
       </c>
@@ -9338,7 +9372,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>39</v>
       </c>
@@ -9361,7 +9395,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>39</v>
       </c>
@@ -9384,7 +9418,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>39</v>
       </c>
@@ -9407,7 +9441,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>39</v>
       </c>
@@ -9430,7 +9464,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>39</v>
       </c>
@@ -9453,7 +9487,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>39</v>
       </c>
@@ -9476,7 +9510,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>39</v>
       </c>
@@ -9499,7 +9533,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>39</v>
       </c>
@@ -9522,7 +9556,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>39</v>
       </c>
@@ -9545,7 +9579,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="284" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>39</v>
       </c>
@@ -9568,7 +9602,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="285" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>39</v>
       </c>
@@ -9591,7 +9625,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="286" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>39</v>
       </c>
@@ -9660,7 +9694,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="289" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>39</v>
       </c>
@@ -9683,7 +9717,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="290" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>39</v>
       </c>
@@ -9706,7 +9740,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="291" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>39</v>
       </c>
@@ -9729,7 +9763,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="292" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>39</v>
       </c>
@@ -9752,7 +9786,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="293" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>39</v>
       </c>
@@ -9775,7 +9809,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="294" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>39</v>
       </c>
@@ -9798,7 +9832,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="295" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>39</v>
       </c>
@@ -9821,7 +9855,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="296" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>39</v>
       </c>
@@ -9844,7 +9878,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="297" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>39</v>
       </c>
@@ -9867,7 +9901,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="298" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>39</v>
       </c>
@@ -9890,7 +9924,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="299" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>39</v>
       </c>
@@ -9913,7 +9947,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="300" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>39</v>
       </c>
@@ -9936,7 +9970,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="301" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>39</v>
       </c>
@@ -9959,7 +9993,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="302" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>39</v>
       </c>
@@ -9982,7 +10016,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="303" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>39</v>
       </c>
@@ -10005,7 +10039,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="304" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>39</v>
       </c>
@@ -10028,7 +10062,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="305" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>39</v>
       </c>
@@ -10051,7 +10085,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="306" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>39</v>
       </c>
@@ -10074,7 +10108,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="307" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>39</v>
       </c>
@@ -10097,7 +10131,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="308" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>39</v>
       </c>
@@ -10120,7 +10154,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="309" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>39</v>
       </c>
@@ -10143,7 +10177,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="310" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>39</v>
       </c>
@@ -10212,7 +10246,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="313" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>39</v>
       </c>
@@ -10237,13 +10271,10 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:G313" xr:uid="{9375A35C-8A58-4D70-9436-2E641DE51D25}">
-    <filterColumn colId="1">
+    <filterColumn colId="2">
       <filters>
-        <filter val="BOAK 2 of 6 Orders"/>
-        <filter val="BOAK 3 of 6 Orders"/>
-        <filter val="BOAK 4 of 6 Orders"/>
-        <filter val="BOAK 5 of 6 Orders"/>
-        <filter val="BOAK 6 Orders"/>
+        <filter val="om_fixed"/>
+        <filter val="om_variable"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -10259,7 +10290,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08421A62-7A7F-4754-940E-DE21752714F2}">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
@@ -10366,6 +10397,28 @@
       </c>
       <c r="D7" t="s">
         <v>72</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" t="s">
+        <v>158</v>
       </c>
     </row>
   </sheetData>
